--- a/artfynd/A 26140-2022 artfynd.xlsx
+++ b/artfynd/A 26140-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26140-2022 artfynd.xlsx
+++ b/artfynd/A 26140-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89565082</v>
+        <v>362574</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergvattnet, Jmt</t>
+          <t>Svansjön 1:5, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509267.8180661423</v>
+        <v>509404</v>
       </c>
       <c r="R2" t="n">
-        <v>7156195.945362771</v>
+        <v>7155997</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,78 +756,68 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89565131</v>
+        <v>900998</v>
       </c>
       <c r="B3" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergvattnet, Jmt</t>
+          <t>Svansjön 1:5, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509361.1330550619</v>
+        <v>509061</v>
       </c>
       <c r="R3" t="n">
-        <v>7156126.920324444</v>
+        <v>7156186</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,31 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89565069</v>
+        <v>89565070</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509388.0972780421</v>
+        <v>509370</v>
       </c>
       <c r="R4" t="n">
-        <v>7156188.99538979</v>
+        <v>7156069</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,21 +945,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,11 +958,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sälg, grov</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1033,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89565109</v>
+        <v>89565079</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509177.0062000881</v>
+        <v>509175</v>
       </c>
       <c r="R5" t="n">
-        <v>7156150.898532447</v>
+        <v>7156132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,21 +1046,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1132,7 +1062,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1154,37 +1084,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89565104</v>
+        <v>89565080</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509407.9179356439</v>
+        <v>509104</v>
       </c>
       <c r="R6" t="n">
-        <v>7156191.209041409</v>
+        <v>7156151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,21 +1152,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1250,6 +1165,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89565089</v>
+        <v>89565082</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509174.9081022912</v>
+        <v>509268</v>
       </c>
       <c r="R7" t="n">
-        <v>7156131.950099467</v>
+        <v>7156196</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,19 +1258,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,37 +1296,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89565083</v>
+        <v>89565092</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509267.8180661423</v>
+        <v>509070</v>
       </c>
       <c r="R8" t="n">
-        <v>7156195.945362771</v>
+        <v>7156166</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,19 +1364,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,15 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89565092</v>
+        <v>89565101</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509070.0636509939</v>
+        <v>509404</v>
       </c>
       <c r="R9" t="n">
-        <v>7156166.076122464</v>
+        <v>7156187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,19 +1470,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,15 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89565070</v>
+        <v>89565133</v>
       </c>
       <c r="B10" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509369.9326245936</v>
+        <v>509388</v>
       </c>
       <c r="R10" t="n">
-        <v>7156068.828694197</v>
+        <v>7156189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,19 +1576,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,15 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89565137</v>
+        <v>89565136</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509363.8754840487</v>
+        <v>509365</v>
       </c>
       <c r="R11" t="n">
-        <v>7156076.128774045</v>
+        <v>7156112</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,19 +1677,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,37 +1710,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89565110</v>
+        <v>89565137</v>
       </c>
       <c r="B12" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1905,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509363.8635699843</v>
+        <v>509364</v>
       </c>
       <c r="R12" t="n">
-        <v>7156080.003342099</v>
+        <v>7156076</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,21 +1778,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1961,11 +1791,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1986,37 +1811,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89565117</v>
+        <v>89561397</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2026,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509359.9775590851</v>
+        <v>509191</v>
       </c>
       <c r="R13" t="n">
-        <v>7156082.143951351</v>
+        <v>7156188</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2059,21 +1879,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2082,11 +1892,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2107,37 +1912,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89565134</v>
+        <v>89565064</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2147,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509383.9249621202</v>
+        <v>509426</v>
       </c>
       <c r="R14" t="n">
-        <v>7156144.210615901</v>
+        <v>7156072</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,19 +1980,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,15 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89565071</v>
+        <v>89565131</v>
       </c>
       <c r="B15" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,21 +2024,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2263,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509363.8635699843</v>
+        <v>509361</v>
       </c>
       <c r="R15" t="n">
-        <v>7156080.003342099</v>
+        <v>7156127</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2296,21 +2081,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2319,11 +2094,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2344,53 +2114,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89565127</v>
+        <v>1868153</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergvattnet, Jmt</t>
+          <t>Svansjön 1:5, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509376.8386309263</v>
+        <v>509039</v>
       </c>
       <c r="R16" t="n">
-        <v>7156065.836359159</v>
+        <v>7156191</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2414,22 +2179,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2444,53 +2199,48 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89565129</v>
+        <v>89565068</v>
       </c>
       <c r="B17" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2500,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509369.9326245936</v>
+        <v>509201</v>
       </c>
       <c r="R17" t="n">
-        <v>7156068.828694197</v>
+        <v>7156172</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2533,21 +2283,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2556,11 +2296,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2581,37 +2316,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89565068</v>
+        <v>89565105</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2621,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509201.0803544777</v>
+        <v>509389</v>
       </c>
       <c r="R18" t="n">
-        <v>7156172.065664731</v>
+        <v>7156207</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2654,21 +2384,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2677,6 +2397,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Björk, högstubbe</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2697,15 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89565105</v>
+        <v>1897618</v>
       </c>
       <c r="B19" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,37 +2433,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergvattnet, Jmt</t>
+          <t>Svansjön 1:5, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509388.9035866269</v>
+        <v>509353</v>
       </c>
       <c r="R19" t="n">
-        <v>7156207.078654764</v>
+        <v>7156035</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2767,22 +2487,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,78 +2503,68 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Björk, högstubbe</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89565122</v>
+        <v>1994499</v>
       </c>
       <c r="B20" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergvattnet, Jmt</t>
+          <t>Svansjön 1:5, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509385.944789713</v>
+        <v>509064</v>
       </c>
       <c r="R20" t="n">
-        <v>7156188.127762212</v>
+        <v>7156194</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2888,22 +2588,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2914,62 +2604,52 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Sälg, grov</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89565116</v>
+        <v>89565069</v>
       </c>
       <c r="B21" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2979,10 +2659,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509201.0803544777</v>
+        <v>509388</v>
       </c>
       <c r="R21" t="n">
-        <v>7156172.065664731</v>
+        <v>7156189</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,21 +2692,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3035,6 +2705,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sälg, grov</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3055,37 +2730,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89565093</v>
+        <v>89565089</v>
       </c>
       <c r="B22" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3095,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509246.8855950491</v>
+        <v>509175</v>
       </c>
       <c r="R22" t="n">
-        <v>7156275.952728116</v>
+        <v>7156132</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3128,21 +2798,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3151,6 +2811,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3171,15 +2836,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89565132</v>
+        <v>89565117</v>
       </c>
       <c r="B23" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3187,21 +2847,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3211,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509420.7933217993</v>
+        <v>509360</v>
       </c>
       <c r="R23" t="n">
-        <v>7156069.846639021</v>
+        <v>7156082</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3244,21 +2904,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3267,6 +2917,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3287,15 +2942,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89565102</v>
+        <v>2071574</v>
       </c>
       <c r="B24" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3323,17 +2973,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergvattnet, Jmt</t>
+          <t>Svansjön 1:5, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509168.0089262967</v>
+        <v>509066</v>
       </c>
       <c r="R24" t="n">
-        <v>7156132.790327962</v>
+        <v>7156195</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3357,22 +3007,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3383,62 +3023,52 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Sälglåga</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89565080</v>
+        <v>89565071</v>
       </c>
       <c r="B25" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3448,10 +3078,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509104.1601981217</v>
+        <v>509364</v>
       </c>
       <c r="R25" t="n">
-        <v>7156151.110371386</v>
+        <v>7156080</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3481,21 +3111,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3507,7 +3127,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3529,37 +3149,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89565133</v>
+        <v>89565083</v>
       </c>
       <c r="B26" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3569,10 +3184,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509388.0972780421</v>
+        <v>509268</v>
       </c>
       <c r="R26" t="n">
-        <v>7156188.99538979</v>
+        <v>7156196</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3602,21 +3217,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3625,6 +3230,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3645,37 +3255,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89565136</v>
+        <v>89565102</v>
       </c>
       <c r="B27" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3685,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509365.0587283864</v>
+        <v>509168</v>
       </c>
       <c r="R27" t="n">
-        <v>7156111.86469174</v>
+        <v>7156133</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3718,21 +3323,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3741,6 +3336,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Sälglåga</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3761,15 +3361,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89561397</v>
+        <v>89565129</v>
       </c>
       <c r="B28" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3777,21 +3372,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3801,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509191.1185688881</v>
+        <v>509370</v>
       </c>
       <c r="R28" t="n">
-        <v>7156187.963972921</v>
+        <v>7156069</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3834,21 +3429,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3857,6 +3442,11 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3877,53 +3467,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89565079</v>
+        <v>2025913</v>
       </c>
       <c r="B29" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergvattnet, Jmt</t>
+          <t>Svansjön 1:5, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509174.9081022912</v>
+        <v>509340</v>
       </c>
       <c r="R29" t="n">
-        <v>7156131.950099467</v>
+        <v>7156035</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3947,22 +3532,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3973,62 +3548,52 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>89565101</v>
+        <v>89565110</v>
       </c>
       <c r="B30" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4038,10 +3603,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509404.0519773093</v>
+        <v>509364</v>
       </c>
       <c r="R30" t="n">
-        <v>7156186.892139602</v>
+        <v>7156080</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4071,19 +3636,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4119,37 +3674,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>89565076</v>
+        <v>89565122</v>
       </c>
       <c r="B31" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4159,10 +3709,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509307.9378301602</v>
+        <v>509386</v>
       </c>
       <c r="R31" t="n">
-        <v>7156184.874844395</v>
+        <v>7156188</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4192,26 +3742,11 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4220,6 +3755,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Sälg, grov</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4233,6 +3773,516 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>89565076</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bergvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>509308</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7156185</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>89565093</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bergvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>509247</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7156276</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>89561417</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bergvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>509184</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7156094</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>89565104</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bergvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>509408</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7156191</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>89565116</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bergvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>509201</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7156172</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 26140-2022 artfynd.xlsx
+++ b/artfynd/A 26140-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/362574</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/900998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565079</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565080</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565082</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565092</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565101</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565133</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565136</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565137</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1909,6 +1969,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561397</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2010,6 +2075,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565064</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2111,6 +2181,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565131</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2212,6 +2287,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1868153</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2313,6 +2393,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565068</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2419,6 +2504,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565105</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2520,6 +2610,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1897618</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2621,6 +2716,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1994499</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2727,6 +2827,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565069</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2833,6 +2938,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565089</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2939,6 +3049,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565117</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3040,6 +3155,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2071574</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3146,6 +3266,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565071</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3252,6 +3377,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565083</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3358,6 +3488,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565102</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3464,6 +3599,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565129</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3565,6 +3705,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2025913</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3671,6 +3816,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565110</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3777,6 +3927,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565122</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3883,6 +4038,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565076</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3984,6 +4144,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565093</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4085,6 +4250,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89561417</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4186,6 +4356,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565104</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4287,8 +4462,50 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565116</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>